--- a/TrackProBackend/static/report/Attendancereport.xlsx
+++ b/TrackProBackend/static/report/Attendancereport.xlsx
@@ -470,17 +470,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M002/1001</t>
+          <t>--</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>maheshkattale1926 gmail</t>
+          <t>Mahesh Kattale</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Software devloper</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -504,12 +509,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ram Patel</t>
+          <t>Prathemash  Kale</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hr</t>
+          <t>Software devloper</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -533,22 +538,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Z001/1001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>zentrotechnologies gmail</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>--</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>User name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hr</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HR</t>
         </is>
       </c>
       <c r="F5" t="n">
